--- a/excel/Aufgaben.xlsx
+++ b/excel/Aufgaben.xlsx
@@ -5,27 +5,30 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Selim\Downloads\Praxisnachbereitung-WS26-27\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youne\OneDrive\Desktop\Praxisnachbereitung-WS26-27\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1EC04D-5DA9-4F82-A60D-C74869C1CF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98386C7E-7F5D-4FC9-BAC7-63D54BB60554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9AA44CF-0CF4-4BAE-B56E-FD76FAE18FF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Mitarbeiter" sheetId="4" r:id="rId1"/>
     <sheet name="Geraete" sheetId="3" r:id="rId2"/>
-    <sheet name="Ausleihen_und_Geraete" sheetId="5" r:id="rId3"/>
-    <sheet name="Ausleihen" sheetId="2" r:id="rId4"/>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId5"/>
+    <sheet name="PivotTabelle" sheetId="7" r:id="rId3"/>
+    <sheet name="Ausleihen_und_Geraete" sheetId="5" r:id="rId4"/>
+    <sheet name="Ausleihen" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExterneDaten_1" localSheetId="3" hidden="1">Ausleihen!$A$1:$D$46</definedName>
-    <definedName name="ExterneDaten_2" localSheetId="2" hidden="1">Ausleihen_und_Geraete!$A$1:$L$46</definedName>
+    <definedName name="ExterneDaten_1" localSheetId="4" hidden="1">Ausleihen!$A$1:$D$46</definedName>
+    <definedName name="ExterneDaten_2" localSheetId="3" hidden="1">Ausleihen_und_Geraete!$A$1:$L$46</definedName>
     <definedName name="ExterneDaten_2" localSheetId="1" hidden="1">Geraete!$A$1:$F$36</definedName>
     <definedName name="ExterneDaten_3" localSheetId="0" hidden="1">Mitarbeiter!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="134">
   <si>
     <t>Gerätenummer</t>
   </si>
@@ -453,6 +456,21 @@
   </si>
   <si>
     <t>Mitarbeiter.Standort</t>
+  </si>
+  <si>
+    <t>Nicht im Einsatz</t>
+  </si>
+  <si>
+    <t>Zeilenbeschriftungen</t>
+  </si>
+  <si>
+    <t>Gesamtergebnis</t>
+  </si>
+  <si>
+    <t>Anzahl von Gerätenummer</t>
+  </si>
+  <si>
+    <t>Spaltenbeschriftungen</t>
   </si>
 </sst>
 </file>
@@ -494,42 +512,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -569,6 +564,36 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -580,6 +605,2062 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Aufgaben.xlsx]PivotTabelle!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTabelle!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Berlin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTabelle!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Beamer</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Drucker</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Smartphone</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTabelle!$B$5:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-75E4-4E81-8DE0-4727780657D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTabelle!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hamburg</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTabelle!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Beamer</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Drucker</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Smartphone</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTabelle!$C$5:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-75E4-4E81-8DE0-4727780657D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTabelle!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>München</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTabelle!$A$5:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Beamer</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Drucker</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Smartphone</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTabelle!$D$5:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-75E4-4E81-8DE0-4727780657D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="377483887"/>
+        <c:axId val="2095422223"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="377483887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2095422223"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2095422223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="377483887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D141D9B7-6F41-A8D6-C87A-BD5D66313329}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Youness Anakhli" refreshedDate="46305.654684953704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{3CF61123-4302-4C0A-BC4E-BC2E0488AE5D}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Gesamt"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="Gerätenummer" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Mitarbeiter-ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1012"/>
+    </cacheField>
+    <cacheField name="Ausgabe am" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-12-01T00:00:00" maxDate="2025-10-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Rückgabe am" numFmtId="14">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2024-06-27T00:00:00" maxDate="2025-10-06T00:00:00"/>
+    </cacheField>
+    <cacheField name="Geraete.Gerätetyp.1" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Beamer"/>
+        <s v="Drucker"/>
+        <s v="Laptop"/>
+        <s v="Monitor"/>
+        <s v="Smartphone"/>
+        <s v="Tablet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Geraete.Modell.1" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Geraete.Kaufdatum.1" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Geraete.Netto-Kaufpreis.1" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="501.64" maxValue="1898.65"/>
+    </cacheField>
+    <cacheField name="Geraete.Standort.1" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Berlin"/>
+        <s v="München"/>
+        <s v="Hamburg"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Mitarbeiter.Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Mitarbeiter.Abteilung" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Mitarbeiter.Standort" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
+  <r>
+    <s v="G0035"/>
+    <n v="1009"/>
+    <d v="2024-05-09T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.01.2024"/>
+    <n v="644.54"/>
+    <x v="0"/>
+    <s v="Univ.Prof. Heimo Karge"/>
+    <s v="Marketing"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0005"/>
+    <n v="1009"/>
+    <d v="2024-04-07T00:00:00"/>
+    <m/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="03.11.2021"/>
+    <n v="823.23"/>
+    <x v="0"/>
+    <s v="Univ.Prof. Heimo Karge"/>
+    <s v="Marketing"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0035"/>
+    <n v="1001"/>
+    <d v="2024-01-06T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.01.2024"/>
+    <n v="644.54"/>
+    <x v="0"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0035"/>
+    <n v="1003"/>
+    <d v="2024-05-05T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.01.2024"/>
+    <n v="644.54"/>
+    <x v="0"/>
+    <s v="Paul Dobes-Stiffel"/>
+    <s v="Produktion"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0016"/>
+    <n v="1003"/>
+    <d v="2024-02-08T00:00:00"/>
+    <d v="2025-06-09T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="30.03.2023"/>
+    <n v="1501.06"/>
+    <x v="0"/>
+    <s v="Paul Dobes-Stiffel"/>
+    <s v="Produktion"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0004"/>
+    <n v="1003"/>
+    <d v="2025-06-19T00:00:00"/>
+    <d v="2025-09-08T00:00:00"/>
+    <x v="2"/>
+    <s v="Dell XPS"/>
+    <s v="05.05.2025"/>
+    <n v="1007.88"/>
+    <x v="1"/>
+    <s v="Paul Dobes-Stiffel"/>
+    <s v="Produktion"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0016"/>
+    <n v="1002"/>
+    <d v="2025-05-22T00:00:00"/>
+    <d v="2025-05-31T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="30.03.2023"/>
+    <n v="1501.06"/>
+    <x v="0"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0021"/>
+    <n v="1008"/>
+    <d v="2025-09-30T00:00:00"/>
+    <d v="2025-10-05T00:00:00"/>
+    <x v="3"/>
+    <s v="Samsung Curved"/>
+    <s v="22.02.2023"/>
+    <n v="1134.1600000000001"/>
+    <x v="1"/>
+    <s v="Dipl.-Ing. Klaus-Werner Holsten B.Sc."/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0024"/>
+    <n v="1008"/>
+    <d v="2024-03-24T00:00:00"/>
+    <m/>
+    <x v="3"/>
+    <s v="Dell UltraSharp"/>
+    <s v="01.03.2022"/>
+    <n v="750.91"/>
+    <x v="0"/>
+    <s v="Dipl.-Ing. Klaus-Werner Holsten B.Sc."/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0024"/>
+    <n v="1005"/>
+    <d v="2025-03-27T00:00:00"/>
+    <d v="2025-07-30T00:00:00"/>
+    <x v="3"/>
+    <s v="Dell UltraSharp"/>
+    <s v="01.03.2022"/>
+    <n v="750.91"/>
+    <x v="0"/>
+    <s v="Alexandre Davids"/>
+    <s v="Vertrieb"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0005"/>
+    <n v="1006"/>
+    <d v="2025-08-23T00:00:00"/>
+    <d v="2025-09-22T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="03.11.2021"/>
+    <n v="823.23"/>
+    <x v="0"/>
+    <s v="Eric Patberg B.Sc."/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0016"/>
+    <n v="1010"/>
+    <d v="2025-07-28T00:00:00"/>
+    <m/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="30.03.2023"/>
+    <n v="1501.06"/>
+    <x v="0"/>
+    <s v="Carolin Hande"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0006"/>
+    <n v="1012"/>
+    <d v="2025-05-31T00:00:00"/>
+    <d v="2025-06-10T00:00:00"/>
+    <x v="4"/>
+    <s v="Samsung S21"/>
+    <s v="01.01.2024"/>
+    <n v="1257.96"/>
+    <x v="1"/>
+    <s v="Ariane Klemt-Kaul"/>
+    <s v="IT"/>
+    <s v="München"/>
+  </r>
+  <r>
+    <s v="G0005"/>
+    <n v="1012"/>
+    <d v="2024-11-03T00:00:00"/>
+    <m/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="03.11.2021"/>
+    <n v="823.23"/>
+    <x v="0"/>
+    <s v="Ariane Klemt-Kaul"/>
+    <s v="IT"/>
+    <s v="München"/>
+  </r>
+  <r>
+    <s v="G0009"/>
+    <n v="1011"/>
+    <d v="2025-07-12T00:00:00"/>
+    <d v="2025-07-15T00:00:00"/>
+    <x v="2"/>
+    <s v="Dell XPS"/>
+    <s v="10.04.2023"/>
+    <n v="1458.02"/>
+    <x v="1"/>
+    <s v="Auguste Davids"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0007"/>
+    <n v="1001"/>
+    <d v="2024-09-09T00:00:00"/>
+    <d v="2025-07-16T00:00:00"/>
+    <x v="2"/>
+    <s v="Lenovo ThinkPad"/>
+    <s v="13.06.2021"/>
+    <n v="869.09"/>
+    <x v="2"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0007"/>
+    <n v="1001"/>
+    <d v="2025-08-11T00:00:00"/>
+    <m/>
+    <x v="2"/>
+    <s v="Lenovo ThinkPad"/>
+    <s v="13.06.2021"/>
+    <n v="869.09"/>
+    <x v="2"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0011"/>
+    <n v="1005"/>
+    <d v="2025-06-29T00:00:00"/>
+    <d v="2025-08-29T00:00:00"/>
+    <x v="1"/>
+    <s v="Brother HL"/>
+    <s v="09.09.2025"/>
+    <n v="1417.1"/>
+    <x v="1"/>
+    <s v="Alexandre Davids"/>
+    <s v="Vertrieb"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0028"/>
+    <n v="1004"/>
+    <d v="2024-08-19T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="19.01.2023"/>
+    <n v="1246.58"/>
+    <x v="2"/>
+    <s v="Klemens Löffler"/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0028"/>
+    <n v="1006"/>
+    <d v="2024-12-04T00:00:00"/>
+    <d v="2025-03-16T00:00:00"/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="19.01.2023"/>
+    <n v="1246.58"/>
+    <x v="2"/>
+    <s v="Eric Patberg B.Sc."/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0028"/>
+    <n v="1003"/>
+    <d v="2024-10-30T00:00:00"/>
+    <d v="2024-12-04T00:00:00"/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="19.01.2023"/>
+    <n v="1246.58"/>
+    <x v="2"/>
+    <s v="Paul Dobes-Stiffel"/>
+    <s v="Produktion"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0013"/>
+    <n v="1012"/>
+    <d v="2024-05-07T00:00:00"/>
+    <d v="2024-06-27T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="16.05.2021"/>
+    <n v="1898.65"/>
+    <x v="2"/>
+    <s v="Ariane Klemt-Kaul"/>
+    <s v="IT"/>
+    <s v="München"/>
+  </r>
+  <r>
+    <s v="G0013"/>
+    <n v="1009"/>
+    <d v="2024-01-28T00:00:00"/>
+    <d v="2025-02-26T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="16.05.2021"/>
+    <n v="1898.65"/>
+    <x v="2"/>
+    <s v="Univ.Prof. Heimo Karge"/>
+    <s v="Marketing"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0029"/>
+    <n v="1002"/>
+    <d v="2025-09-21T00:00:00"/>
+    <d v="2025-10-04T00:00:00"/>
+    <x v="2"/>
+    <s v="Lenovo ThinkPad"/>
+    <s v="21.05.2021"/>
+    <n v="1553.15"/>
+    <x v="2"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0015"/>
+    <n v="1010"/>
+    <d v="2024-03-26T00:00:00"/>
+    <d v="2025-08-17T00:00:00"/>
+    <x v="4"/>
+    <s v="iPhone 13"/>
+    <s v="20.09.2022"/>
+    <n v="661.44"/>
+    <x v="1"/>
+    <s v="Carolin Hande"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0015"/>
+    <n v="1002"/>
+    <d v="2024-08-15T00:00:00"/>
+    <m/>
+    <x v="4"/>
+    <s v="iPhone 13"/>
+    <s v="20.09.2022"/>
+    <n v="661.44"/>
+    <x v="1"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0022"/>
+    <n v="1002"/>
+    <d v="2025-08-30T00:00:00"/>
+    <d v="2025-09-30T00:00:00"/>
+    <x v="5"/>
+    <s v="iPad"/>
+    <s v="20.08.2024"/>
+    <n v="1591.98"/>
+    <x v="2"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0022"/>
+    <n v="1002"/>
+    <d v="2024-07-20T00:00:00"/>
+    <d v="2025-01-06T00:00:00"/>
+    <x v="5"/>
+    <s v="iPad"/>
+    <s v="20.08.2024"/>
+    <n v="1591.98"/>
+    <x v="2"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0018"/>
+    <n v="1011"/>
+    <d v="2024-10-03T00:00:00"/>
+    <d v="2024-11-27T00:00:00"/>
+    <x v="5"/>
+    <s v="iPad"/>
+    <s v="05.10.2022"/>
+    <n v="1688.07"/>
+    <x v="1"/>
+    <s v="Auguste Davids"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0031"/>
+    <n v="1004"/>
+    <d v="2024-01-29T00:00:00"/>
+    <m/>
+    <x v="2"/>
+    <s v="HP EliteBook"/>
+    <s v="28.04.2025"/>
+    <n v="1095.6199999999999"/>
+    <x v="1"/>
+    <s v="Klemens Löffler"/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0031"/>
+    <n v="1004"/>
+    <d v="2024-02-14T00:00:00"/>
+    <m/>
+    <x v="2"/>
+    <s v="HP EliteBook"/>
+    <s v="28.04.2025"/>
+    <n v="1095.6199999999999"/>
+    <x v="1"/>
+    <s v="Klemens Löffler"/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0027"/>
+    <n v="1004"/>
+    <d v="2024-04-21T00:00:00"/>
+    <d v="2025-07-01T00:00:00"/>
+    <x v="3"/>
+    <s v="Samsung Curved"/>
+    <s v="24.07.2022"/>
+    <n v="501.64"/>
+    <x v="1"/>
+    <s v="Klemens Löffler"/>
+    <s v="Vertrieb"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0030"/>
+    <n v="1012"/>
+    <d v="2025-05-15T00:00:00"/>
+    <d v="2025-09-05T00:00:00"/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="27.03.2022"/>
+    <n v="1629.76"/>
+    <x v="1"/>
+    <s v="Ariane Klemt-Kaul"/>
+    <s v="IT"/>
+    <s v="München"/>
+  </r>
+  <r>
+    <s v="G0030"/>
+    <n v="1005"/>
+    <d v="2023-12-01T00:00:00"/>
+    <d v="2024-09-24T00:00:00"/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="27.03.2022"/>
+    <n v="1629.76"/>
+    <x v="1"/>
+    <s v="Alexandre Davids"/>
+    <s v="Vertrieb"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0025"/>
+    <n v="1005"/>
+    <d v="2025-01-18T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="Epson EB"/>
+    <s v="06.12.2023"/>
+    <n v="545.46"/>
+    <x v="0"/>
+    <s v="Alexandre Davids"/>
+    <s v="Vertrieb"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0032"/>
+    <n v="1003"/>
+    <d v="2024-08-04T00:00:00"/>
+    <d v="2025-08-02T00:00:00"/>
+    <x v="2"/>
+    <s v="Lenovo ThinkPad"/>
+    <s v="11.11.2022"/>
+    <n v="1801.36"/>
+    <x v="1"/>
+    <s v="Paul Dobes-Stiffel"/>
+    <s v="Produktion"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0014"/>
+    <n v="1001"/>
+    <d v="2024-11-26T00:00:00"/>
+    <d v="2025-03-03T00:00:00"/>
+    <x v="2"/>
+    <s v="Lenovo ThinkPad"/>
+    <s v="03.03.2021"/>
+    <n v="1415.97"/>
+    <x v="2"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0035"/>
+    <n v="1001"/>
+    <d v="2024-12-15T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.01.2024"/>
+    <n v="644.54"/>
+    <x v="0"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0004"/>
+    <n v="1001"/>
+    <d v="2025-08-11T00:00:00"/>
+    <d v="2025-08-12T00:00:00"/>
+    <x v="2"/>
+    <s v="Dell XPS"/>
+    <s v="05.05.2025"/>
+    <n v="1007.88"/>
+    <x v="1"/>
+    <s v="Aleksandr Weinhage"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0033"/>
+    <n v="1009"/>
+    <d v="2025-03-24T00:00:00"/>
+    <d v="2025-05-07T00:00:00"/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.03.2022"/>
+    <n v="1212.29"/>
+    <x v="0"/>
+    <s v="Univ.Prof. Heimo Karge"/>
+    <s v="Marketing"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0033"/>
+    <n v="1002"/>
+    <d v="2025-03-25T00:00:00"/>
+    <m/>
+    <x v="0"/>
+    <s v="BenQ MW550"/>
+    <s v="03.03.2022"/>
+    <n v="1212.29"/>
+    <x v="0"/>
+    <s v="Eleni Hauffer"/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0005"/>
+    <n v="1010"/>
+    <d v="2025-08-30T00:00:00"/>
+    <d v="2025-09-25T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="03.11.2021"/>
+    <n v="823.23"/>
+    <x v="0"/>
+    <s v="Carolin Hande"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0016"/>
+    <n v="1007"/>
+    <d v="2025-05-18T00:00:00"/>
+    <d v="2025-07-08T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="30.03.2023"/>
+    <n v="1501.06"/>
+    <x v="0"/>
+    <s v="Orhan Siering MBA."/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+  <r>
+    <s v="G0016"/>
+    <n v="1010"/>
+    <d v="2025-05-31T00:00:00"/>
+    <d v="2025-10-02T00:00:00"/>
+    <x v="1"/>
+    <s v="Canon Pixma"/>
+    <s v="30.03.2023"/>
+    <n v="1501.06"/>
+    <x v="0"/>
+    <s v="Carolin Hande"/>
+    <s v="IT"/>
+    <s v="Hamburg"/>
+  </r>
+  <r>
+    <s v="G0006"/>
+    <n v="1007"/>
+    <d v="2024-07-03T00:00:00"/>
+    <m/>
+    <x v="4"/>
+    <s v="Samsung S21"/>
+    <s v="01.01.2024"/>
+    <n v="1257.96"/>
+    <x v="1"/>
+    <s v="Orhan Siering MBA."/>
+    <s v="IT"/>
+    <s v="Berlin"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91308064-23DE-44D6-A746-7FA6107D9706}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl von Gerätenummer" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,14 +2678,15 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExterneDaten_2" connectionId="2" xr16:uid="{38938B1C-DBD3-4953-AE2B-6FB505D3AE42}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="Gerätenummer" tableColumnId="1"/>
       <queryTableField id="2" name="Gerätetyp" tableColumnId="2"/>
       <queryTableField id="3" name="Modell" tableColumnId="3"/>
       <queryTableField id="4" name="Kaufdatum" tableColumnId="4"/>
       <queryTableField id="5" name="Netto-Kaufpreis" tableColumnId="5"/>
       <queryTableField id="6" name="Standort" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -649,24 +2731,27 @@
   <autoFilter ref="A1:D13" xr:uid="{8BB108E9-5E7A-42D9-BCB7-EEFB1C6C11C3}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4111BAC4-C86A-4908-9BBE-8341137F56F5}" uniqueName="1" name="Mitarbeiter-ID" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{7CAA53F1-DAD3-42DB-BF3F-187E805EC56A}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{69F9E89A-C6BD-470E-94D0-23B2679DD242}" uniqueName="3" name="Abteilung" queryTableFieldId="3" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{C9125458-EB2C-4B52-8B87-CE81351C6500}" uniqueName="4" name="Standort" queryTableFieldId="4" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{7CAA53F1-DAD3-42DB-BF3F-187E805EC56A}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{69F9E89A-C6BD-470E-94D0-23B2679DD242}" uniqueName="3" name="Abteilung" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{C9125458-EB2C-4B52-8B87-CE81351C6500}" uniqueName="4" name="Standort" queryTableFieldId="4" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}" name="Geraete" displayName="Geraete" ref="A1:F36" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F36" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C9683A72-B1D3-4323-964F-5262C920D13A}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{4BDB1687-CEEC-45F6-9020-42E9440A0A99}" uniqueName="2" name="Gerätetyp" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{C74385E5-16BF-4B23-ADC7-5EC4F06B0BB6}" uniqueName="3" name="Modell" queryTableFieldId="3" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{FB4F2C3C-45D1-4D00-8100-96E6518C5693}" uniqueName="4" name="Kaufdatum" queryTableFieldId="4" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{30F140D4-1EA5-4E15-BA43-D9CF26089CD2}" uniqueName="5" name="Netto-Kaufpreis" queryTableFieldId="5" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{5B927673-1BE7-460C-8C41-5AA92686167B}" uniqueName="6" name="Standort" queryTableFieldId="6" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}" name="Geraete" displayName="Geraete" ref="A1:G36" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G36" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C9683A72-B1D3-4323-964F-5262C920D13A}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4BDB1687-CEEC-45F6-9020-42E9440A0A99}" uniqueName="2" name="Gerätetyp" queryTableFieldId="2" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{C74385E5-16BF-4B23-ADC7-5EC4F06B0BB6}" uniqueName="3" name="Modell" queryTableFieldId="3" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{FB4F2C3C-45D1-4D00-8100-96E6518C5693}" uniqueName="4" name="Kaufdatum" queryTableFieldId="4" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{30F140D4-1EA5-4E15-BA43-D9CF26089CD2}" uniqueName="5" name="Netto-Kaufpreis" queryTableFieldId="5" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{5B927673-1BE7-460C-8C41-5AA92686167B}" uniqueName="6" name="Standort" queryTableFieldId="6" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{9DE3A97F-2045-45C4-A0C4-8A2FD68E8C1F}" uniqueName="7" name="Nicht im Einsatz" queryTableFieldId="7" dataDxfId="0">
+      <calculatedColumnFormula>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -676,18 +2761,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B6384748-8BAB-4008-81B3-839D0EDB8EED}" name="Gesamt" displayName="Gesamt" ref="A1:L46" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:L46" xr:uid="{B6384748-8BAB-4008-81B3-839D0EDB8EED}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C018294C-D41A-473A-8F50-32046682BEDF}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{C018294C-D41A-473A-8F50-32046682BEDF}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{9BA7042B-B525-4C8C-AEDD-96D112FEF2FC}" uniqueName="2" name="Mitarbeiter-ID" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{13B21C29-BD40-4DE3-84E5-022CFF803F59}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{DB158027-8904-4874-829D-526384628D4C}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{C4F653E7-26E8-45C5-BE7E-F53D8826EFD1}" uniqueName="10" name="Geraete.Gerätetyp.1" queryTableFieldId="10" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{28BA945A-8AE9-4C16-A397-040174C51F17}" uniqueName="11" name="Geraete.Modell.1" queryTableFieldId="11" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{5228F3A2-CCA0-449C-B982-8B73A8D0E5F2}" uniqueName="12" name="Geraete.Kaufdatum.1" queryTableFieldId="12" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{13B21C29-BD40-4DE3-84E5-022CFF803F59}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{DB158027-8904-4874-829D-526384628D4C}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{C4F653E7-26E8-45C5-BE7E-F53D8826EFD1}" uniqueName="10" name="Geraete.Gerätetyp.1" queryTableFieldId="10" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{28BA945A-8AE9-4C16-A397-040174C51F17}" uniqueName="11" name="Geraete.Modell.1" queryTableFieldId="11" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{5228F3A2-CCA0-449C-B982-8B73A8D0E5F2}" uniqueName="12" name="Geraete.Kaufdatum.1" queryTableFieldId="12" dataDxfId="17"/>
     <tableColumn id="13" xr3:uid="{10D5FFC4-12F3-453B-B5BF-957063871887}" uniqueName="13" name="Geraete.Netto-Kaufpreis.1" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{44DA6073-8872-42A8-B2C0-DCB4FA1E0D84}" uniqueName="14" name="Geraete.Standort.1" queryTableFieldId="14" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{AAB1C294-AA9B-4C8A-ABB4-08AE2DC9777D}" uniqueName="15" name="Mitarbeiter.Name" queryTableFieldId="15" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{B71E9ACD-D0B8-456A-9CA6-96314292CB8E}" uniqueName="16" name="Mitarbeiter.Abteilung" queryTableFieldId="16" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{78334E36-D8F9-4008-BC3B-DB7477B80E90}" uniqueName="17" name="Mitarbeiter.Standort" queryTableFieldId="17" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{44DA6073-8872-42A8-B2C0-DCB4FA1E0D84}" uniqueName="14" name="Geraete.Standort.1" queryTableFieldId="14" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{AAB1C294-AA9B-4C8A-ABB4-08AE2DC9777D}" uniqueName="15" name="Mitarbeiter.Name" queryTableFieldId="15" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{B71E9ACD-D0B8-456A-9CA6-96314292CB8E}" uniqueName="16" name="Mitarbeiter.Abteilung" queryTableFieldId="16" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{78334E36-D8F9-4008-BC3B-DB7477B80E90}" uniqueName="17" name="Mitarbeiter.Standort" queryTableFieldId="17" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -697,10 +2782,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9726D9-FA38-4B94-90B1-132F61F700B3}" name="Ausleihen" displayName="Ausleihen" ref="A1:D46" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:D46" xr:uid="{9C9726D9-FA38-4B94-90B1-132F61F700B3}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12E77856-A536-4320-BB4C-88C3DBFA26B3}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{12E77856-A536-4320-BB4C-88C3DBFA26B3}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{83C7E2CB-7B47-48BE-AF78-D3CDCBB2759F}" uniqueName="2" name="Mitarbeiter-ID" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{C2390173-CBAF-49C9-B2FB-CB581A74FF9E}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{ABF2AAB3-A561-489E-AD63-E731DF39B56D}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{C2390173-CBAF-49C9-B2FB-CB581A74FF9E}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{ABF2AAB3-A561-489E-AD63-E731DF39B56D}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1050,13 +3135,13 @@
       <c r="A2">
         <v>1001</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1064,13 +3149,13 @@
       <c r="A3">
         <v>1002</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1078,13 +3163,13 @@
       <c r="A4">
         <v>1003</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1092,13 +3177,13 @@
       <c r="A5">
         <v>1004</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1106,13 +3191,13 @@
       <c r="A6">
         <v>1005</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1120,13 +3205,13 @@
       <c r="A7">
         <v>1006</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1134,13 +3219,13 @@
       <c r="A8">
         <v>1007</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1148,13 +3233,13 @@
       <c r="A9">
         <v>1008</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1162,13 +3247,13 @@
       <c r="A10">
         <v>1009</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1176,13 +3261,13 @@
       <c r="A11">
         <v>1010</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1190,13 +3275,13 @@
       <c r="A12">
         <v>1011</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1204,13 +3289,13 @@
       <c r="A13">
         <v>1012</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1224,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DF632A-A668-44CB-822E-C9B19364D764}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -1234,7 +3319,7 @@
     <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1253,705 +3338,856 @@
       <c r="F1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>1342.83</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="G2" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(Geraete[Nicht im Einsatz],"Ja")</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>1076.18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="G3" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>1931.54</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="G4" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF(Geraete[Nicht im Einsatz],"Ja",Geraete[Netto-Kaufpreis])</f>
+        <v>33239.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>1007.88</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="G5" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>823.23</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="G6" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>1257.96</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="G7" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>869.09</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="G8" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>1323.76</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="G9" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>1458.02</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="G10" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>1786.37</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="G11" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>1417.1</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="G12" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>968.43</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="G13" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>1898.65</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="G14" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>1415.97</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="G15" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>661.44</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="G16" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>1501.06</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="G17" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>1748.56</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="G18" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>1688.07</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="G19" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <v>737.57</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="G20" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <v>740.2</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="G21" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22">
         <v>1134.1600000000001</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="G22" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23">
         <v>1591.98</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="G23" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24">
         <v>1335.34</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="G24" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25">
         <v>750.91</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="G25" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26">
         <v>545.46</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="G26" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27">
         <v>1403.91</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="G27" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28">
         <v>501.64</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="G28" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29">
         <v>1246.58</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="G29" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30">
         <v>1553.15</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="G30" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31">
         <v>1629.76</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="G31" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32">
         <v>1095.6199999999999</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="G32" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>97</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33">
         <v>1801.36</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="G33" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>99</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34">
         <v>1212.29</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="G34" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>100</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35">
         <v>1746.67</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="G35" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>102</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36">
         <v>644.54</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>36</v>
+      </c>
+      <c r="G36" s="2" t="str">
+        <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
+        <v>Nein</v>
       </c>
     </row>
   </sheetData>
@@ -1963,6 +4199,158 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39ABC340-6E69-4D30-BD19-C214E73CFA76}">
+  <dimension ref="A3:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="2">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB51707E-64B3-439E-AF84-6B83160F074F}">
   <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2024,1680 +4412,1680 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <v>1009</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>45421</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>102</v>
       </c>
       <c r="H2">
         <v>644.54</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>116</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>117</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
         <v>1009</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>45389</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>49</v>
       </c>
       <c r="H3">
         <v>823.23</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>116</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>117</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>1001</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>45297</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>102</v>
       </c>
       <c r="H4">
         <v>644.54</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>105</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>106</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <v>1003</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>45417</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>102</v>
       </c>
       <c r="H5">
         <v>644.54</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>108</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>109</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
         <v>1003</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>45330</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>45817</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>71</v>
       </c>
       <c r="H6">
         <v>1501.06</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>45827</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>45908</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>46</v>
       </c>
       <c r="H7">
         <v>1007.88</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>108</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>109</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
         <v>1002</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>45799</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>45808</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>71</v>
       </c>
       <c r="H8">
         <v>1501.06</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9">
         <v>1008</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>45930</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>45935</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>82</v>
       </c>
       <c r="H9">
         <v>1134.1600000000001</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>115</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>106</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10">
         <v>1008</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>45375</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>87</v>
       </c>
       <c r="H10">
         <v>750.91</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>115</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>106</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
       <c r="B11">
         <v>1005</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>45743</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>45868</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>87</v>
       </c>
       <c r="H11">
         <v>750.91</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12">
         <v>1006</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>45892</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>45922</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>49</v>
       </c>
       <c r="H12">
         <v>823.23</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>113</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>7</v>
       </c>
       <c r="B13">
         <v>1010</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>45866</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>71</v>
       </c>
       <c r="H13">
         <v>1501.06</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>118</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14">
         <v>1012</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>45808</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>45818</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>52</v>
       </c>
       <c r="H14">
         <v>1257.96</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>120</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>106</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15">
         <v>1012</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>45599</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>49</v>
       </c>
       <c r="H15">
         <v>823.23</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>120</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>106</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
       <c r="B16">
         <v>1011</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>45850</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>45853</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>60</v>
       </c>
       <c r="H16">
         <v>1458.02</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>106</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17">
         <v>1001</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>45544</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>45854</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>54</v>
       </c>
       <c r="H17">
         <v>869.09</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18">
         <v>1001</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>45880</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>54</v>
       </c>
       <c r="H18">
         <v>869.09</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>106</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>11</v>
       </c>
       <c r="B19">
         <v>1005</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>45837</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>45898</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>64</v>
       </c>
       <c r="H19">
         <v>1417.1</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>112</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>111</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>12</v>
       </c>
       <c r="B20">
         <v>1004</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>45523</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="1"/>
+      <c r="E20" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>92</v>
       </c>
       <c r="H20">
         <v>1246.58</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>110</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>111</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21">
         <v>1006</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>45630</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>45732</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>92</v>
       </c>
       <c r="H21">
         <v>1246.58</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>113</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>111</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22">
         <v>1003</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>45595</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>45630</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>92</v>
       </c>
       <c r="H22">
         <v>1246.58</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>55</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>108</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>109</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23">
         <v>1012</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>45419</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>45470</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>67</v>
       </c>
       <c r="H23">
         <v>1898.65</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>120</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>106</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24">
         <v>1009</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>45319</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>45714</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>67</v>
       </c>
       <c r="H24">
         <v>1898.65</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>55</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>117</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>14</v>
       </c>
       <c r="B25">
         <v>1002</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>45921</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>45934</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>93</v>
       </c>
       <c r="H25">
         <v>1553.15</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>107</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>106</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26">
         <v>1010</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>45377</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>45886</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>69</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>70</v>
       </c>
       <c r="H26">
         <v>661.44</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>40</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>118</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>106</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>15</v>
       </c>
       <c r="B27">
         <v>1002</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>45519</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>69</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>70</v>
       </c>
       <c r="H27">
         <v>661.44</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>40</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>107</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>106</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>16</v>
       </c>
       <c r="B28">
         <v>1002</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="1">
         <v>45899</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>45930</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>83</v>
       </c>
       <c r="H28">
         <v>1591.98</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>107</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" t="s">
         <v>106</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>16</v>
       </c>
       <c r="B29">
         <v>1002</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>45493</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>45663</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>83</v>
       </c>
       <c r="H29">
         <v>1591.98</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>55</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>107</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" t="s">
         <v>106</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="L29" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>17</v>
       </c>
       <c r="B30">
         <v>1011</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>45568</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>45623</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>74</v>
       </c>
       <c r="H30">
         <v>1688.07</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>119</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" t="s">
         <v>106</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>18</v>
       </c>
       <c r="B31">
         <v>1004</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>45320</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="1"/>
+      <c r="E31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>95</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>96</v>
       </c>
       <c r="H31">
         <v>1095.6199999999999</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>110</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" t="s">
         <v>111</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>18</v>
       </c>
       <c r="B32">
         <v>1004</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>45336</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="1" t="s">
+      <c r="D32" s="1"/>
+      <c r="E32" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>96</v>
       </c>
       <c r="H32">
         <v>1095.6199999999999</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>110</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>111</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="L32" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>19</v>
       </c>
       <c r="B33">
         <v>1004</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="1">
         <v>45403</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>45839</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" t="s">
         <v>80</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>91</v>
       </c>
       <c r="H33">
         <v>501.64</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>110</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" t="s">
         <v>111</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="L33" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>20</v>
       </c>
       <c r="B34">
         <v>1012</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>45792</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>45905</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>58</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>94</v>
       </c>
       <c r="H34">
         <v>1629.76</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" t="s">
         <v>40</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>120</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" t="s">
         <v>106</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>20</v>
       </c>
       <c r="B35">
         <v>1005</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>45261</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>45559</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>58</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>94</v>
       </c>
       <c r="H35">
         <v>1629.76</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" t="s">
         <v>40</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>112</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" t="s">
         <v>111</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>23</v>
       </c>
       <c r="B36">
         <v>1005</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>45675</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="1" t="s">
+      <c r="D36" s="1"/>
+      <c r="E36" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>58</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>88</v>
       </c>
       <c r="H36">
         <v>545.46</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>112</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" t="s">
         <v>111</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>24</v>
       </c>
       <c r="B37">
         <v>1003</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>45508</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>45871</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" t="s">
         <v>44</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" t="s">
         <v>53</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>97</v>
       </c>
       <c r="H37">
         <v>1801.36</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>40</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>108</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" t="s">
         <v>109</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="L37" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>25</v>
       </c>
       <c r="B38">
         <v>1001</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
         <v>45622</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>45719</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" t="s">
         <v>53</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>68</v>
       </c>
       <c r="H38">
         <v>1415.97</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>55</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>105</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" t="s">
         <v>106</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="L38" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>4</v>
       </c>
       <c r="B39">
         <v>1001</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>45641</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="1" t="s">
+      <c r="D39" s="1"/>
+      <c r="E39" t="s">
         <v>57</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>102</v>
       </c>
       <c r="H39">
         <v>644.54</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>36</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>105</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" t="s">
         <v>106</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="L39" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>22</v>
       </c>
       <c r="B40">
         <v>1001</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
         <v>45880</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>45881</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>45</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>46</v>
       </c>
       <c r="H40">
         <v>1007.88</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>40</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>105</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" t="s">
         <v>106</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="L40" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>26</v>
       </c>
       <c r="B41">
         <v>1009</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="1">
         <v>45740</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>45784</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" t="s">
         <v>98</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>99</v>
       </c>
       <c r="H41">
         <v>1212.29</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>116</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" t="s">
         <v>117</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="L41" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>26</v>
       </c>
       <c r="B42">
         <v>1002</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="1">
         <v>45741</v>
       </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="1" t="s">
+      <c r="D42" s="1"/>
+      <c r="E42" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" t="s">
         <v>98</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>99</v>
       </c>
       <c r="H42">
         <v>1212.29</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>36</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>107</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" t="s">
         <v>106</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L42" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
       <c r="B43">
         <v>1010</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>45899</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>45925</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" t="s">
         <v>48</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>49</v>
       </c>
       <c r="H43">
         <v>823.23</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" t="s">
         <v>36</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>118</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" t="s">
         <v>106</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="L43" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
       <c r="B44">
         <v>1007</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>45795</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>45846</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" t="s">
         <v>48</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>71</v>
       </c>
       <c r="H44">
         <v>1501.06</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" t="s">
         <v>114</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" t="s">
         <v>106</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="L44" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>7</v>
       </c>
       <c r="B45">
         <v>1010</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="1">
         <v>45808</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>45932</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" t="s">
         <v>47</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" t="s">
         <v>48</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>71</v>
       </c>
       <c r="H45">
         <v>1501.06</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>118</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" t="s">
         <v>106</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="L45" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
       <c r="B46">
         <v>1007</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="1">
         <v>45476</v>
       </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="1" t="s">
+      <c r="D46" s="1"/>
+      <c r="E46" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>52</v>
       </c>
       <c r="H46">
         <v>1257.96</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>114</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" t="s">
         <v>106</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="L46" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3710,7 +6098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8955EC7A-1D79-47E7-A4F9-FD567EA5E5BD}">
   <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3736,602 +6124,602 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
         <v>1009</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>45421</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
         <v>1008</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>45930</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>45935</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
         <v>1005</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>45743</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>45868</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
         <v>1010</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>45866</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
         <v>1012</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>45808</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>45818</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7">
         <v>1009</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>45389</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
         <v>1011</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>45850</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>45853</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>45837</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>45898</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10">
         <v>1004</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>45523</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
         <v>1012</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>45419</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>45470</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>45375</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <v>1002</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>45921</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>45934</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14">
         <v>1006</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>45892</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>45922</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>45377</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>45886</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>45599</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17">
         <v>1002</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>45519</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18">
         <v>1002</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>45899</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>45930</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19">
         <v>1011</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>45568</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>45623</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20">
         <v>1003</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>45417</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
       <c r="B21">
         <v>1004</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>45320</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
       <c r="B22">
         <v>1004</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>45403</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>45839</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23">
         <v>1006</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>45630</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>45732</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>20</v>
       </c>
       <c r="B24">
         <v>1012</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>45792</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>45905</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="B25">
         <v>1001</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>45544</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>45854</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>16</v>
       </c>
       <c r="B26">
         <v>1002</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>45493</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <v>45663</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27">
         <v>1009</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>45319</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>45714</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>12</v>
       </c>
       <c r="B28">
         <v>1003</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="1">
         <v>45595</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="1">
         <v>45630</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>7</v>
       </c>
       <c r="B29">
         <v>1002</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>45799</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>45808</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>21</v>
       </c>
       <c r="B30">
         <v>1001</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>45880</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
       <c r="B31">
         <v>1001</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>45297</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>7</v>
       </c>
       <c r="B32">
         <v>1003</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>45330</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>45817</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>18</v>
       </c>
       <c r="B33">
         <v>1004</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="1">
         <v>45336</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>22</v>
       </c>
       <c r="B34">
         <v>1003</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>45827</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>45908</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>23</v>
       </c>
       <c r="B35">
         <v>1005</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>45675</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>20</v>
       </c>
       <c r="B36">
         <v>1005</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>45261</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>45559</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>24</v>
       </c>
       <c r="B37">
         <v>1003</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>45508</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>45871</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>25</v>
       </c>
       <c r="B38">
         <v>1001</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
         <v>45622</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="1">
         <v>45719</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>4</v>
       </c>
       <c r="B39">
         <v>1001</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>45641</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>22</v>
       </c>
       <c r="B40">
         <v>1001</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
         <v>45880</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="1">
         <v>45881</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>26</v>
       </c>
       <c r="B41">
         <v>1009</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="1">
         <v>45740</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="1">
         <v>45784</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>26</v>
       </c>
       <c r="B42">
         <v>1002</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="1">
         <v>45741</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
       <c r="B43">
         <v>1010</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>45899</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>45925</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
       <c r="B44">
         <v>1007</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>45795</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="1">
         <v>45846</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>7</v>
       </c>
       <c r="B45">
         <v>1010</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="1">
         <v>45808</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>45932</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
       <c r="B46">
         <v>1007</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="1">
         <v>45476</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4339,15 +6727,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAF6242-AF1B-4E0E-93D0-E57E15EE1A1F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/excel/Aufgaben.xlsx
+++ b/excel/Aufgaben.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youne\OneDrive\Desktop\Praxisnachbereitung-WS26-27\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98386C7E-7F5D-4FC9-BAC7-63D54BB60554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAF4D40-6956-4E11-97D0-F2B84063BF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9AA44CF-0CF4-4BAE-B56E-FD76FAE18FF3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9AA44CF-0CF4-4BAE-B56E-FD76FAE18FF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Mitarbeiter" sheetId="4" r:id="rId1"/>
     <sheet name="Geraete" sheetId="3" r:id="rId2"/>
     <sheet name="PivotTabelle" sheetId="7" r:id="rId3"/>
-    <sheet name="Ausleihen_und_Geraete" sheetId="5" r:id="rId4"/>
+    <sheet name="Gesamt" sheetId="5" r:id="rId4"/>
     <sheet name="Ausleihen" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="ExterneDaten_1" localSheetId="4" hidden="1">Ausleihen!$A$1:$D$46</definedName>
-    <definedName name="ExterneDaten_2" localSheetId="3" hidden="1">Ausleihen_und_Geraete!$A$1:$L$46</definedName>
     <definedName name="ExterneDaten_2" localSheetId="1" hidden="1">Geraete!$A$1:$F$36</definedName>
+    <definedName name="ExterneDaten_2" localSheetId="3" hidden="1">Gesamt!$A$1:$L$46</definedName>
     <definedName name="ExterneDaten_3" localSheetId="0" hidden="1">Mitarbeiter!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -512,10 +512,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -525,6 +524,33 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -563,33 +589,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -741,6 +740,62 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -2537,7 +2592,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91308064-23DE-44D6-A746-7FA6107D9706}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91308064-23DE-44D6-A746-7FA6107D9706}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:E11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -2616,7 +2671,7 @@
   <dataFields count="1">
     <dataField name="Anzahl von Gerätenummer" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="3">
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -2646,6 +2701,18 @@
           </reference>
           <reference field="8" count="1" selected="0">
             <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -2731,9 +2798,9 @@
   <autoFilter ref="A1:D13" xr:uid="{8BB108E9-5E7A-42D9-BCB7-EEFB1C6C11C3}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4111BAC4-C86A-4908-9BBE-8341137F56F5}" uniqueName="1" name="Mitarbeiter-ID" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{7CAA53F1-DAD3-42DB-BF3F-187E805EC56A}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{69F9E89A-C6BD-470E-94D0-23B2679DD242}" uniqueName="3" name="Abteilung" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{C9125458-EB2C-4B52-8B87-CE81351C6500}" uniqueName="4" name="Standort" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7CAA53F1-DAD3-42DB-BF3F-187E805EC56A}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{69F9E89A-C6BD-470E-94D0-23B2679DD242}" uniqueName="3" name="Abteilung" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{C9125458-EB2C-4B52-8B87-CE81351C6500}" uniqueName="4" name="Standort" queryTableFieldId="4" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2743,13 +2810,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}" name="Geraete" displayName="Geraete" ref="A1:G36" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G36" xr:uid="{D75EDBB6-9DEA-431F-A79F-4F010F154E72}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C9683A72-B1D3-4323-964F-5262C920D13A}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{4BDB1687-CEEC-45F6-9020-42E9440A0A99}" uniqueName="2" name="Gerätetyp" queryTableFieldId="2" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{C74385E5-16BF-4B23-ADC7-5EC4F06B0BB6}" uniqueName="3" name="Modell" queryTableFieldId="3" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{FB4F2C3C-45D1-4D00-8100-96E6518C5693}" uniqueName="4" name="Kaufdatum" queryTableFieldId="4" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{30F140D4-1EA5-4E15-BA43-D9CF26089CD2}" uniqueName="5" name="Netto-Kaufpreis" queryTableFieldId="5" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{5B927673-1BE7-460C-8C41-5AA92686167B}" uniqueName="6" name="Standort" queryTableFieldId="6" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{9DE3A97F-2045-45C4-A0C4-8A2FD68E8C1F}" uniqueName="7" name="Nicht im Einsatz" queryTableFieldId="7" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{C9683A72-B1D3-4323-964F-5262C920D13A}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{4BDB1687-CEEC-45F6-9020-42E9440A0A99}" uniqueName="2" name="Gerätetyp" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{C74385E5-16BF-4B23-ADC7-5EC4F06B0BB6}" uniqueName="3" name="Modell" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{FB4F2C3C-45D1-4D00-8100-96E6518C5693}" uniqueName="4" name="Kaufdatum" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{30F140D4-1EA5-4E15-BA43-D9CF26089CD2}" uniqueName="5" name="Netto-Kaufpreis" queryTableFieldId="5" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{5B927673-1BE7-460C-8C41-5AA92686167B}" uniqueName="6" name="Standort" queryTableFieldId="6" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{9DE3A97F-2045-45C4-A0C4-8A2FD68E8C1F}" uniqueName="7" name="Nicht im Einsatz" queryTableFieldId="7" dataDxfId="13">
       <calculatedColumnFormula>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2761,18 +2828,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B6384748-8BAB-4008-81B3-839D0EDB8EED}" name="Gesamt" displayName="Gesamt" ref="A1:L46" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:L46" xr:uid="{B6384748-8BAB-4008-81B3-839D0EDB8EED}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C018294C-D41A-473A-8F50-32046682BEDF}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{C018294C-D41A-473A-8F50-32046682BEDF}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{9BA7042B-B525-4C8C-AEDD-96D112FEF2FC}" uniqueName="2" name="Mitarbeiter-ID" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{13B21C29-BD40-4DE3-84E5-022CFF803F59}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{DB158027-8904-4874-829D-526384628D4C}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{C4F653E7-26E8-45C5-BE7E-F53D8826EFD1}" uniqueName="10" name="Geraete.Gerätetyp.1" queryTableFieldId="10" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{28BA945A-8AE9-4C16-A397-040174C51F17}" uniqueName="11" name="Geraete.Modell.1" queryTableFieldId="11" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{5228F3A2-CCA0-449C-B982-8B73A8D0E5F2}" uniqueName="12" name="Geraete.Kaufdatum.1" queryTableFieldId="12" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{13B21C29-BD40-4DE3-84E5-022CFF803F59}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{DB158027-8904-4874-829D-526384628D4C}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{C4F653E7-26E8-45C5-BE7E-F53D8826EFD1}" uniqueName="10" name="Geraete.Gerätetyp.1" queryTableFieldId="10" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{28BA945A-8AE9-4C16-A397-040174C51F17}" uniqueName="11" name="Geraete.Modell.1" queryTableFieldId="11" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{5228F3A2-CCA0-449C-B982-8B73A8D0E5F2}" uniqueName="12" name="Geraete.Kaufdatum.1" queryTableFieldId="12" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{10D5FFC4-12F3-453B-B5BF-957063871887}" uniqueName="13" name="Geraete.Netto-Kaufpreis.1" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{44DA6073-8872-42A8-B2C0-DCB4FA1E0D84}" uniqueName="14" name="Geraete.Standort.1" queryTableFieldId="14" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{AAB1C294-AA9B-4C8A-ABB4-08AE2DC9777D}" uniqueName="15" name="Mitarbeiter.Name" queryTableFieldId="15" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{B71E9ACD-D0B8-456A-9CA6-96314292CB8E}" uniqueName="16" name="Mitarbeiter.Abteilung" queryTableFieldId="16" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{78334E36-D8F9-4008-BC3B-DB7477B80E90}" uniqueName="17" name="Mitarbeiter.Standort" queryTableFieldId="17" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{44DA6073-8872-42A8-B2C0-DCB4FA1E0D84}" uniqueName="14" name="Geraete.Standort.1" queryTableFieldId="14" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{AAB1C294-AA9B-4C8A-ABB4-08AE2DC9777D}" uniqueName="15" name="Mitarbeiter.Name" queryTableFieldId="15" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{B71E9ACD-D0B8-456A-9CA6-96314292CB8E}" uniqueName="16" name="Mitarbeiter.Abteilung" queryTableFieldId="16" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{78334E36-D8F9-4008-BC3B-DB7477B80E90}" uniqueName="17" name="Mitarbeiter.Standort" queryTableFieldId="17" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2782,10 +2849,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9726D9-FA38-4B94-90B1-132F61F700B3}" name="Ausleihen" displayName="Ausleihen" ref="A1:D46" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:D46" xr:uid="{9C9726D9-FA38-4B94-90B1-132F61F700B3}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12E77856-A536-4320-BB4C-88C3DBFA26B3}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{12E77856-A536-4320-BB4C-88C3DBFA26B3}" uniqueName="1" name="Gerätenummer" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{83C7E2CB-7B47-48BE-AF78-D3CDCBB2759F}" uniqueName="2" name="Mitarbeiter-ID" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{C2390173-CBAF-49C9-B2FB-CB581A74FF9E}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{ABF2AAB3-A561-489E-AD63-E731DF39B56D}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{C2390173-CBAF-49C9-B2FB-CB581A74FF9E}" uniqueName="3" name="Ausgabe am" queryTableFieldId="3" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{ABF2AAB3-A561-489E-AD63-E731DF39B56D}" uniqueName="4" name="Rückgabe am" queryTableFieldId="4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3361,7 +3428,7 @@
       <c r="F2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2" t="str">
+      <c r="G2" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3389,7 +3456,7 @@
       <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="2" t="str">
+      <c r="G3" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3413,7 +3480,7 @@
       <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="2" t="str">
+      <c r="G4" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3441,7 +3508,7 @@
       <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="str">
+      <c r="G5" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3465,7 +3532,7 @@
       <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="str">
+      <c r="G6" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3489,7 +3556,7 @@
       <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="2" t="str">
+      <c r="G7" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3513,7 +3580,7 @@
       <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="2" t="str">
+      <c r="G8" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3537,7 +3604,7 @@
       <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="2" t="str">
+      <c r="G9" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3561,7 +3628,7 @@
       <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="2" t="str">
+      <c r="G10" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3585,7 +3652,7 @@
       <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="2" t="str">
+      <c r="G11" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3609,7 +3676,7 @@
       <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="2" t="str">
+      <c r="G12" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3633,7 +3700,7 @@
       <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="2" t="str">
+      <c r="G13" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3657,7 +3724,7 @@
       <c r="F14" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="2" t="str">
+      <c r="G14" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3681,7 +3748,7 @@
       <c r="F15" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="2" t="str">
+      <c r="G15" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3705,7 +3772,7 @@
       <c r="F16" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="2" t="str">
+      <c r="G16" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3729,7 +3796,7 @@
       <c r="F17" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="2" t="str">
+      <c r="G17" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3753,7 +3820,7 @@
       <c r="F18" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="2" t="str">
+      <c r="G18" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3777,7 +3844,7 @@
       <c r="F19" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="2" t="str">
+      <c r="G19" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3801,7 +3868,7 @@
       <c r="F20" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="2" t="str">
+      <c r="G20" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3825,7 +3892,7 @@
       <c r="F21" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="2" t="str">
+      <c r="G21" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3849,7 +3916,7 @@
       <c r="F22" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="2" t="str">
+      <c r="G22" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3873,7 +3940,7 @@
       <c r="F23" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="2" t="str">
+      <c r="G23" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3897,7 +3964,7 @@
       <c r="F24" t="s">
         <v>55</v>
       </c>
-      <c r="G24" s="2" t="str">
+      <c r="G24" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3921,7 +3988,7 @@
       <c r="F25" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="2" t="str">
+      <c r="G25" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3945,7 +4012,7 @@
       <c r="F26" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="2" t="str">
+      <c r="G26" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -3969,7 +4036,7 @@
       <c r="F27" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="2" t="str">
+      <c r="G27" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -3993,7 +4060,7 @@
       <c r="F28" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="2" t="str">
+      <c r="G28" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -4017,7 +4084,7 @@
       <c r="F29" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="2" t="str">
+      <c r="G29" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -4041,7 +4108,7 @@
       <c r="F30" t="s">
         <v>55</v>
       </c>
-      <c r="G30" s="2" t="str">
+      <c r="G30" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -4065,7 +4132,7 @@
       <c r="F31" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="2" t="str">
+      <c r="G31" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -4089,7 +4156,7 @@
       <c r="F32" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="2" t="str">
+      <c r="G32" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -4113,7 +4180,7 @@
       <c r="F33" t="s">
         <v>40</v>
       </c>
-      <c r="G33" s="2" t="str">
+      <c r="G33" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -4137,7 +4204,7 @@
       <c r="F34" t="s">
         <v>36</v>
       </c>
-      <c r="G34" s="2" t="str">
+      <c r="G34" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -4161,7 +4228,7 @@
       <c r="F35" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="2" t="str">
+      <c r="G35" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Ja</v>
       </c>
@@ -4185,7 +4252,7 @@
       <c r="F36" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="2" t="str">
+      <c r="G36" t="str">
         <f>IF(COUNTIFS(Ausleihen[Gerätenummer],Geraete[[#This Row],[Gerätenummer]],Ausleihen[Rückgabe am],"")=0,"Ja","Nein")</f>
         <v>Nein</v>
       </c>
@@ -4211,15 +4278,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B4" t="s">
@@ -4236,111 +4303,106 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>7</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>18</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>11</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11">
         <v>16</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
         <v>45</v>
       </c>
     </row>
